--- a/data/DatosGrafica_AdquirirQ1_20260530_195139.xlsx
+++ b/data/DatosGrafica_AdquirirQ1_20260530_195139.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectosPropios\learningTesting\testeos\ModeloTermicoBjt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE71B47F-D90D-4AA7-AD9B-21B5873634F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4657A4-3798-43B4-B3F4-44E17960BC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Tiempo</t>
   </si>
@@ -33,16 +44,36 @@
   <si>
     <t>PWM1</t>
   </si>
+  <si>
+    <t>FODPT</t>
+  </si>
+  <si>
+    <t>Kgain</t>
+  </si>
+  <si>
+    <t>tau/ts</t>
+  </si>
+  <si>
+    <t>td</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -66,8 +97,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,10 +445,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1007"/>
+  <dimension ref="A1:N1007"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>39</v>
       </c>
@@ -444,7 +476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>41</v>
       </c>
@@ -458,7 +490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>41</v>
       </c>
@@ -472,7 +504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>42</v>
       </c>
@@ -486,7 +518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>43</v>
       </c>
@@ -500,7 +532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>45</v>
       </c>
@@ -514,7 +546,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>45</v>
       </c>
@@ -528,7 +560,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>46</v>
       </c>
@@ -542,7 +574,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>47</v>
       </c>
@@ -556,7 +588,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>49</v>
       </c>
@@ -570,7 +602,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>49</v>
       </c>
@@ -584,7 +616,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>50</v>
       </c>
@@ -597,8 +629,11 @@
       <c r="D13">
         <v>50</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="N13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>51</v>
       </c>
@@ -611,8 +646,15 @@
       <c r="D14">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="M14" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14">
+        <f>(MAX(B:B)-MIN(B:B))/(_xlfn.MODE.SNGL(D:D)-MIN(D:D))</f>
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>53</v>
       </c>
@@ -625,8 +667,15 @@
       <c r="D15">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="M15" t="s">
+        <v>6</v>
+      </c>
+      <c r="N15">
+        <f>_xlfn.XLOOKUP(MAX(B:B)*0.632,B:B,A:A,"ajustar valor",-1)-_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1)*1</f>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>53</v>
       </c>
@@ -639,8 +688,15 @@
       <c r="D16">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16">
+        <f>_xlfn.XLOOKUP(MIN(B:B)*1.02,B:B,A:A,"cambiar",-1)-(_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>54</v>
       </c>
@@ -654,7 +710,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>55</v>
       </c>
@@ -668,7 +724,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>57</v>
       </c>
@@ -682,7 +738,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>57</v>
       </c>
@@ -695,8 +751,9 @@
       <c r="D20">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>58</v>
       </c>
@@ -710,7 +767,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>59</v>
       </c>
@@ -724,7 +781,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>60</v>
       </c>
@@ -738,7 +795,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>60</v>
       </c>
@@ -752,7 +809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>62</v>
       </c>
@@ -766,7 +823,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>63</v>
       </c>
@@ -780,7 +837,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>64</v>
       </c>
@@ -794,7 +851,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>64</v>
       </c>
@@ -808,7 +865,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>66</v>
       </c>
@@ -822,7 +879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>67</v>
       </c>
@@ -836,7 +893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>68</v>
       </c>
@@ -850,7 +907,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>68</v>
       </c>
@@ -14516,6 +14573,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/DatosGrafica_AdquirirQ1_20260530_195139.xlsx
+++ b/data/DatosGrafica_AdquirirQ1_20260530_195139.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectosPropios\learningTesting\testeos\ModeloTermicoBjt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectoTesis\ModelosBJT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4657A4-3798-43B4-B3F4-44E17960BC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140187A4-D8EE-4B80-83F5-EDA2B1A1ABBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7755" yWindow="2640" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,9 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>247651</xdr:colOff>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3162300" cy="3581400"/>
@@ -147,7 +147,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3657601" y="190500"/>
+          <a:off x="5124451" y="0"/>
           <a:ext cx="3162300" cy="3581400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -448,7 +448,7 @@
   <dimension ref="A1:N1007"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,8 +461,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>39</v>
       </c>
@@ -475,8 +478,19 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f>(MAX(B:B)-MIN(B:B))/(_xlfn.MODE.SNGL(D:D)-MIN(D:D))</f>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H2">
+        <f>(MAX(B:B)-MIN(B:B))/(MODE(D:D)-MIN(D:D))</f>
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>41</v>
       </c>
@@ -489,8 +503,19 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.XLOOKUP(MAX(B:B)*0.632,B:B,A:A,"ajustar valor",-1)-_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1)*1</f>
+        <v>121</v>
+      </c>
+      <c r="H3">
+        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - INDEX(A:A, MATCH(MODE(D:D), D:D, 0))*1</f>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>41</v>
       </c>
@@ -503,8 +528,19 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <f>_xlfn.XLOOKUP(MIN(B:B)*1.02,B:B,A:A,"cambiar",-1)-(_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1))</f>
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <f>INDEX(A:A, MATCH(MIN(B:B)*1.02, B:B)) - (INDEX(A:A, MATCH(MODE(D:D), D:D, 0)))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>42</v>
       </c>
@@ -518,7 +554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>43</v>
       </c>
@@ -532,7 +568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>45</v>
       </c>
@@ -546,7 +582,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>45</v>
       </c>
@@ -560,7 +596,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>46</v>
       </c>
@@ -574,7 +610,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>47</v>
       </c>
@@ -588,7 +624,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>49</v>
       </c>
@@ -602,7 +638,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>49</v>
       </c>
@@ -616,7 +652,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>50</v>
       </c>
@@ -629,11 +665,8 @@
       <c r="D13">
         <v>50</v>
       </c>
-      <c r="N13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>51</v>
       </c>
@@ -646,15 +679,8 @@
       <c r="D14">
         <v>50</v>
       </c>
-      <c r="M14" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14">
-        <f>(MAX(B:B)-MIN(B:B))/(_xlfn.MODE.SNGL(D:D)-MIN(D:D))</f>
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>53</v>
       </c>
@@ -667,15 +693,8 @@
       <c r="D15">
         <v>50</v>
       </c>
-      <c r="M15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N15">
-        <f>_xlfn.XLOOKUP(MAX(B:B)*0.632,B:B,A:A,"ajustar valor",-1)-_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1)*1</f>
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>53</v>
       </c>
@@ -687,13 +706,6 @@
       </c>
       <c r="D16">
         <v>50</v>
-      </c>
-      <c r="M16" t="s">
-        <v>7</v>
-      </c>
-      <c r="N16">
-        <f>_xlfn.XLOOKUP(MIN(B:B)*1.02,B:B,A:A,"cambiar",-1)-(_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1))</f>
-        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
